--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
@@ -19,11 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$E$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
@@ -1083,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1994,8 +1994,26 @@
       </c>
       <c r="D51" s="12" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>For the points of BDOI's FRS covered by a BRD line</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D51"/>
+  <autoFilter ref="A4:D52"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2070,7 +2088,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2080,7 +2098,7 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>SUM('CR Effort'!M5:M8)</f>
+        <f>SUM('CR Effort'!M5:M6)</f>
         <v/>
       </c>
     </row>
@@ -2091,7 +2109,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>SUM('CR Effort'!N5:N8)</f>
+        <f>SUM('CR Effort'!N5:N6)</f>
         <v/>
       </c>
     </row>
@@ -2102,7 +2120,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>SUM('CR Effort'!O5:O8)</f>
+        <f>SUM('CR Effort'!O5:O6)</f>
         <v/>
       </c>
     </row>
@@ -2113,7 +2131,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>SUM('CR Effort'!P5:P8)</f>
+        <f>SUM('CR Effort'!P5:P6)</f>
         <v/>
       </c>
     </row>
@@ -2124,7 +2142,7 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>SUM('CR Effort'!Q5:Q8)</f>
+        <f>SUM('CR Effort'!Q5:Q6)</f>
         <v/>
       </c>
     </row>
@@ -2135,7 +2153,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>SUM('CR Effort'!R5:R8)</f>
+        <f>SUM('CR Effort'!R5:R6)</f>
         <v/>
       </c>
     </row>
@@ -2146,7 +2164,7 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>SUM('CR Effort'!S5:S8)</f>
+        <f>SUM('CR Effort'!S5:S6)</f>
         <v/>
       </c>
     </row>
@@ -2157,7 +2175,7 @@
         </is>
       </c>
       <c r="B14" s="12">
-        <f>SUM('CR Effort'!T5:T8)</f>
+        <f>SUM('CR Effort'!T5:T6)</f>
         <v/>
       </c>
     </row>
@@ -2168,7 +2186,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>SUM('CR Effort'!U5:U8)</f>
+        <f>SUM('CR Effort'!U5:U6)</f>
         <v/>
       </c>
     </row>
@@ -2232,7 +2250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2551,57 +2569,57 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>E-mail to a recipient list when a scheduled Cashiering run fails</t>
+          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>FRS.CSH.10.03; Appendix G (failed batch run)</t>
+          <t>Appendix G (channel of each notice)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>BRQID.006 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Extends a BRD requirement</t>
+          <t>Not in any BRD</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>FRS v3.2 Appendix G (failed batch run notice and its recipients)</t>
+          <t>FRS v3.2 Appendix G (proposed, Appendix R)</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>The BRD asks that users are alerted when a run fails; an e-mail to named recipients makes sure a failed overnight run is seen before the business day starts.</t>
+          <t>Team Leaders who post from branches want the notices also by e-mail; the choice per user and per notice avoids e-mail floods.</t>
         </is>
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>WFL-013 Partial (a failed job raises an in-app notification to the schedule administrators; no e-mail to a recipient list)</t>
+          <t>WFL-011 Available (e-mail notifications from templates); WFL-012 Partial. Disagreement: the Feature List says Available, the OOTB code has no per-user e-mail choice</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>My Work: count of failed jobs; no e-mail to a recipient list</t>
+          <t>Notifications: in-app notices; no per-user choice of an e-mail copy</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Yes: the e-mail to the failed-run recipients setting was prepared for BIBS in this project</t>
+          <t>Yes: the Notification Settings screen of BIBS gives this choice</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (e-mail to a recipient list).</t>
+          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>One mail service and one setting over the job scheduler of the platform.</t>
+          <t>Notification service of the platform; one settings screen.</t>
         </is>
       </c>
       <c r="M6" s="22" t="n">
@@ -2611,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="22" t="n">
         <v>0.5</v>
@@ -2642,7 +2660,7 @@
       </c>
       <c r="W6" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="X6" s="12" t="inlineStr">
@@ -2652,316 +2670,90 @@
       </c>
       <c r="Y6" s="12" t="inlineStr">
         <is>
-          <t>One recipient list setting for all Cashiering runs; the in-app notice stays.</t>
+          <t>Choice per user and per notice type; default in-app only.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>CR-CSH-103</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Excel export of the Cashiering lists</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.01.03.04</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>CSHID.023 (extends)</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Extends a BRD requirement</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>FRS v3.2 FRS.CSH.01.03.04</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Cashiers and Team Leaders work the lists in Excel for reconciliation and follow-up; the BRD asks for extracts of the reports, the FRS extends it to every list.</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>BIL-016 Available (receipts register with filters); RPT-003 Partial. Disagreement: the Feature List says Available, the OOTB code exports the receipt list to PDF only</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>Receipts list: filters and PDF export only (no Excel)</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Yes: the Cashiering lists of BIBS export to Excel</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (Excel export of the lists).</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>List services of the receipts module; export pattern of the reports module.</t>
-        </is>
-      </c>
-      <c r="M7" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P7" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="22" t="n">
-        <v>0.5</v>
+          <t>2 change requests</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="22">
+        <f>SUM(M5:M6)</f>
+        <v/>
+      </c>
+      <c r="N7" s="22">
+        <f>SUM(N5:N6)</f>
+        <v/>
+      </c>
+      <c r="O7" s="22">
+        <f>SUM(O5:O6)</f>
+        <v/>
+      </c>
+      <c r="P7" s="22">
+        <f>SUM(P5:P6)</f>
+        <v/>
+      </c>
+      <c r="Q7" s="22">
+        <f>SUM(Q5:Q6)</f>
+        <v/>
       </c>
       <c r="R7" s="22">
-        <f>SUM(M7:Q7)</f>
+        <f>SUM(R5:R6)</f>
         <v/>
       </c>
       <c r="S7" s="22">
-        <f>ROUND(R7*(1-Assumptions!$B$6),1)</f>
+        <f>SUM(S5:S6)</f>
         <v/>
       </c>
       <c r="T7" s="22">
-        <f>ROUND(R7*(1+Assumptions!$B$6),1)</f>
+        <f>SUM(T5:T6)</f>
         <v/>
       </c>
       <c r="U7" s="23">
-        <f>R7*Assumptions!$B$7</f>
+        <f>SUM(U5:U6)</f>
         <v/>
       </c>
-      <c r="V7" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W7" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="X7" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y7" s="12" t="inlineStr">
-        <is>
-          <t>Same columns as on the screen; up to the report row limit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>CR-CSH-104</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Each user chooses an e-mail copy of the Cashiering notices</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Appendix G (channel of each notice)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Not in any BRD</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>FRS v3.2 Appendix G (proposed, Appendix R)</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Team Leaders who post from branches want the notices also by e-mail; the choice per user and per notice avoids e-mail floods.</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>WFL-011 Available (e-mail notifications from templates); WFL-012 Partial. Disagreement: the Feature List says Available, the OOTB code has no per-user e-mail choice</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>Notifications: in-app notices; no per-user choice of an e-mail copy</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Yes: the Notification Settings screen of BIBS gives this choice</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>Notification service of the platform; one settings screen.</t>
-        </is>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R8" s="22">
-        <f>SUM(M8:Q8)</f>
-        <v/>
-      </c>
-      <c r="S8" s="22">
-        <f>ROUND(R8*(1-Assumptions!$B$6),1)</f>
-        <v/>
-      </c>
-      <c r="T8" s="22">
-        <f>ROUND(R8*(1+Assumptions!$B$6),1)</f>
-        <v/>
-      </c>
-      <c r="U8" s="23">
-        <f>R8*Assumptions!$B$7</f>
-        <v/>
-      </c>
-      <c r="V8" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W8" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="X8" s="12" t="inlineStr">
-        <is>
-          <t>E-mail channel of BDOI</t>
-        </is>
-      </c>
-      <c r="Y8" s="12" t="inlineStr">
-        <is>
-          <t>Choice per user and per notice type; default in-app only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>4 change requests</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="22">
-        <f>SUM(M5:M8)</f>
-        <v/>
-      </c>
-      <c r="N9" s="22">
-        <f>SUM(N5:N8)</f>
-        <v/>
-      </c>
-      <c r="O9" s="22">
-        <f>SUM(O5:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="22">
-        <f>SUM(P5:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="22">
-        <f>SUM(Q5:Q8)</f>
-        <v/>
-      </c>
-      <c r="R9" s="22">
-        <f>SUM(R5:R8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="22">
-        <f>SUM(S5:S8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="22">
-        <f>SUM(T5:T8)</f>
-        <v/>
-      </c>
-      <c r="U9" s="23">
-        <f>SUM(U5:U8)</f>
-        <v/>
-      </c>
-      <c r="V9" s="12" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="12" t="n"/>
-      <c r="Y9" s="12" t="n"/>
+      <c r="V7" s="12" t="n"/>
+      <c r="W7" s="12" t="n"/>
+      <c r="X7" s="12" t="n"/>
+      <c r="Y7" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y9"/>
+  <autoFilter ref="A4:Y7"/>
   <mergeCells count="1">
     <mergeCell ref="A2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:Y509">
+  <conditionalFormatting sqref="A5:Y507">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E5:E509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
+    <dataValidation sqref="E5:E507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="V5:V509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="V5:V507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="W5:W509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="W5:W507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4049,13 +3841,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4077,6 +3870,7 @@
       <c r="B3" s="20" t="n"/>
       <c r="C3" s="20" t="n"/>
       <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -4099,6 +3893,11 @@
           <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -4121,6 +3920,7 @@
           <t>Sign-in, roles and permissions per action and segregation of duties are standard; the Cashiering permissions are given to the roles by configuration (Appendix H).</t>
         </is>
       </c>
+      <c r="E5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -4143,6 +3943,7 @@
           <t>Sign-in, roles and permissions per action and segregation of duties are standard; the Cashiering permissions are given to the roles by configuration (Appendix H).</t>
         </is>
       </c>
+      <c r="E6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -4165,6 +3966,7 @@
           <t>Role home pages with live work counts are standard; the Cashiering dashboard with count and amount per receipt type and status is an extension (the counts are available, the amounts per type follow BDOI's FRS.CSH.01.03.02).</t>
         </is>
       </c>
+      <c r="E7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -4187,6 +3989,7 @@
           <t>File uploads with runs, records and alerts, and the exchanges between the BIBS modules are standard; the MFT intake of the OBPCS and PMS files is an extension to agree with BDOI IT.</t>
         </is>
       </c>
+      <c r="E8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -4209,6 +4012,7 @@
           <t>File uploads with runs, records and alerts, and the exchanges between the BIBS modules are standard; the MFT intake of the OBPCS and PMS files is an extension to agree with BDOI IT.</t>
         </is>
       </c>
+      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -4231,6 +4035,7 @@
           <t>Receipts with payor, references, amount, currency and mode, matched and applied at once, are standard; the posting step by a second user, the entry type and the bank account of BDOI's FRS are extensions (Appendix R, C1).</t>
         </is>
       </c>
+      <c r="E10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -4253,6 +4058,7 @@
           <t>Head Office receipts of income with VAT and withholding tax lines and the income account of each type are standard; the types are a maintained list.</t>
         </is>
       </c>
+      <c r="E11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -4275,6 +4081,7 @@
           <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
         </is>
       </c>
+      <c r="E12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -4297,6 +4104,7 @@
           <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
         </is>
       </c>
+      <c r="E13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -4319,6 +4127,7 @@
           <t>Cancellation and reinstatement as requests with a reason, approved by a second user, with reversal entries, are standard; the remitted / not remitted branches and AP Unapplied Commission of BDOI's FRS are extensions.</t>
         </is>
       </c>
+      <c r="E14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -4341,6 +4150,7 @@
           <t>Series per branch and kind with ATP, range, warning level and maker-checker; numbering under a lock and a depleted-series stop are standard.</t>
         </is>
       </c>
+      <c r="E15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -4363,6 +4173,7 @@
           <t>Commission payment details uploaded and issued as ORs per insurer and certificate are standard; the Commission Schedule matching and the trigger at the Disbursement approval of BDOI's FRS are extensions.</t>
         </is>
       </c>
+      <c r="E16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -4385,6 +4196,7 @@
           <t>Uploads of the channel files with configurable layouts, duplicate refusal and the post-dated check warehouse with its daily maturity are standard; MFT intake, several files per event, file-name and header total checks are extensions.</t>
         </is>
       </c>
+      <c r="E17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -4407,6 +4219,7 @@
           <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
         </is>
       </c>
+      <c r="E18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -4429,6 +4242,7 @@
           <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
         </is>
       </c>
+      <c r="E19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -4451,6 +4265,7 @@
           <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
         </is>
       </c>
+      <c r="E20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -4473,6 +4288,7 @@
           <t>Every Cashiering event posts a balanced journal through rules maintained by Comptrollership; no account is fixed in the system.</t>
         </is>
       </c>
+      <c r="E21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -4495,6 +4311,7 @@
           <t>Series per branch and kind with ATP, range, warning level and maker-checker; numbering under a lock and a depleted-series stop are standard.</t>
         </is>
       </c>
+      <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -4517,6 +4334,7 @@
           <t>Minimal balances cleared when the payment is processed with a configurable threshold and the three exceptions are standard.</t>
         </is>
       </c>
+      <c r="E23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -4539,6 +4357,7 @@
           <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
         </is>
       </c>
+      <c r="E24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -4561,6 +4380,7 @@
           <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
         </is>
       </c>
+      <c r="E25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
@@ -4583,6 +4403,7 @@
           <t>Batch printing of receipts with a print log is standard; the ZIP of single PDFs, the certificate number and the REPRINT mark of BDOI's FRS are extensions.</t>
         </is>
       </c>
+      <c r="E26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -4605,6 +4426,7 @@
           <t>Matching on the account references with pre-booked, excess, unmatched and cancelled-reference outcomes is standard; the legacy numbers as keys and the Direct Credit identification of BDOI's FRS are extensions.</t>
         </is>
       </c>
+      <c r="E27" s="12" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
@@ -4627,6 +4449,7 @@
           <t>Application by component in a fixed order (DST, VAT, LGT, FST, other charges, basic premium), never to the premium due to the insurer.</t>
         </is>
       </c>
+      <c r="E28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -4649,6 +4472,7 @@
           <t>Reports with separate view and export rights and an archive of every run are standard; the layouts of BDOI's FRS.CSH.09.02 are set up as report layouts.</t>
         </is>
       </c>
+      <c r="E29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
@@ -4671,6 +4495,7 @@
           <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
         </is>
       </c>
+      <c r="E30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -4693,6 +4518,7 @@
           <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
         </is>
       </c>
+      <c r="E31" s="12" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
@@ -4715,6 +4541,7 @@
           <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
         </is>
       </c>
+      <c r="E32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -4737,6 +4564,7 @@
           <t>Not offered for Cashiering (check pick-up and the Cashiering BIR 2307 processing are withdrawn).</t>
         </is>
       </c>
+      <c r="E33" s="12" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
@@ -4759,6 +4587,7 @@
           <t>Specified in the FRS of Marketing Collection and Disbursement; Cashiering keeps the PR 2307 outstanding at payment.</t>
         </is>
       </c>
+      <c r="E34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -4781,6 +4610,7 @@
           <t>Specified in the FRS of Marketing Collection and Disbursement; Cashiering keeps the PR 2307 outstanding at payment.</t>
         </is>
       </c>
+      <c r="E35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
@@ -4803,6 +4633,7 @@
           <t>Within the BIBS sizing for all BRDs</t>
         </is>
       </c>
+      <c r="E36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -4825,6 +4656,7 @@
           <t>Assumed within the BIBS sizing; to confirm</t>
         </is>
       </c>
+      <c r="E37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -4847,6 +4679,7 @@
           <t>Screens within 3 seconds for 95% of requests; file processing and printing run in the background with progress</t>
         </is>
       </c>
+      <c r="E38" s="12" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -4869,6 +4702,7 @@
           <t>Print batches of up to 500 receipts</t>
         </is>
       </c>
+      <c r="E39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -4891,6 +4725,7 @@
           <t>Files up to 50 MB; each row processed on its own</t>
         </is>
       </c>
+      <c r="E40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -4913,6 +4748,7 @@
           <t>Runs scheduled outside the peak hours (Appendix M)</t>
         </is>
       </c>
+      <c r="E41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -4935,6 +4771,7 @@
           <t>Same service window as BIBS</t>
         </is>
       </c>
+      <c r="E42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -4957,6 +4794,7 @@
           <t>Programme backup and recovery</t>
         </is>
       </c>
+      <c r="E43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -4979,6 +4817,7 @@
           <t>Retention per record type</t>
         </is>
       </c>
+      <c r="E44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -5001,6 +4840,7 @@
           <t>Responsive screens; BDO-issued devices (FRS.OPS.001)</t>
         </is>
       </c>
+      <c r="E45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -5023,6 +4863,7 @@
           <t>Role-based access, segregation of duties, files stored read-only</t>
         </is>
       </c>
+      <c r="E46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -5045,6 +4886,7 @@
           <t>Audit trail that no user can change, refused actions recorded</t>
         </is>
       </c>
+      <c r="E47" s="12" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -5067,6 +4909,7 @@
           <t>Amounts with thousands separators and two decimals; dates dd-MMM-yyyy; Philippine time</t>
         </is>
       </c>
+      <c r="E48" s="12" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -5089,6 +4932,7 @@
           <t>Parameters and lists of Appendix H changed without a change to the system</t>
         </is>
       </c>
+      <c r="E49" s="12" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -5111,6 +4955,7 @@
           <t>Planned maintenance within the maintenance windows of the bank standard; users told in advance</t>
         </is>
       </c>
+      <c r="E50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -5133,6 +4978,7 @@
           <t>Programme disaster recovery; the targets of CSH-NFR-08 apply</t>
         </is>
       </c>
+      <c r="E51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -5155,6 +5001,7 @@
           <t>A second sign-in on another device ends the first (User Access Maintenance FRS)</t>
         </is>
       </c>
+      <c r="E52" s="12" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -5177,13 +5024,64 @@
           <t>The audit log records the workstation / IP address of every action</t>
         </is>
       </c>
+      <c r="E53" s="12" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>D-CSH-01</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>E-mail to a recipient list when a scheduled Cashiering run fails (FRS.CSH.10.03; Appendix G (failed batch run)). BRD line: BRQID.005 AC5: 'System alerts users in case of failed data fetch or mismatched data'; BRQID.006 batch job processing</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>BRD point to deliver</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>WFL-013 Partial (a failed job raises an in-app notification to the schedule administrators; no e-mail to a recipient list). Partial in BrokerVerse OOTB; the planning effort is that of the missing part (e-mail to a recipient list).</t>
+        </is>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>D-CSH-02</t>
+        </is>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Excel export of the Cashiering lists (FRS.CSH.01.03.04). BRD line: CSHID.017 AC4: 'Download reports in supported formats (e.g., PDF, Excel)'; CSHID.023 'Capability to generate reports'</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>BRD point to deliver</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>BIL-016 Available (receipts register with filters); RPT-003 Partial. Disagreement: the Feature List says Available, the OOTB code exports the receipt list to PDF only. Partial in BrokerVerse OOTB; the planning effort is that of the missing part (Excel export of the lists).</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D53"/>
+  <autoFilter ref="A4:E55"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:D553">
+  <conditionalFormatting sqref="A5:E555">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
@@ -12,28 +12,31 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD covered - OOTB" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$59</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Integration &amp; DM scope'!$A$4:$D$33</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$E$55</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD covered - OOTB'!$A$4:$G$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD covered - OOTB'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integration &amp; DM scope'!$A$4:$D$33</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integration &amp; DM scope'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BRD items to deliver'!$A$4:$E$55</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -364,7 +367,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -677,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E30"/>
+  <dimension ref="B4:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -843,7 +846,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -873,71 +876,86 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Covered by the Integration scope or the Data Migration scope (BRD-13): no CR cost here</t>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse OOTB platform provides: no change request, no effort</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Not in the BRD, the FRS or the OOTB platform: recommendations (Appendix W.6), not commitments</t>
+          <t>Covered by the Integration scope or the Data Migration scope (BRD-13): no CR cost here</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements not fully met by the OOTB platform: in-scope delivery work for planning, not CRs</t>
+          <t>Not in the BRD, the FRS or the OOTB platform: recommendations (Appendix W.6), not commitments</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
         <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully met by the OOTB platform: in-scope delivery work for planning, not CRs</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Man-day, range and day rate used by the formulas</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D28" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="15" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -953,6 +971,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -965,11 +984,199 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Hours in a man-day</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>One man-day (md) = 8 working hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Philippine peso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Estimate range (plus or minus)</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Each total is an estimate within plus or minus 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>DayRate (PHP per man-day)</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Enter the agreed day rate; the cost columns follow by formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>OOTB baseline</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>brokerverse-platform</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Platform size</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Not change requests</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Estimated again if the scope of a change request changes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1083,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1755,17 +1962,17 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Interface or data load</t>
+          <t>Former green point</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -1773,39 +1980,35 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Integration or Data Migration</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Integration scope, Data Migration scope</t>
-        </is>
-      </c>
+          <t>The point of the FRS</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>What is exchanged or loaded</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -1813,17 +2016,17 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Where in the FRS</t>
+          <t>BRD line</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Annex</t>
+          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -1831,17 +2034,17 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Best practice</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -1849,17 +2052,17 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Insurance-broking practice</t>
+          <t>Screen or function of brokerverse-platform</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -1867,17 +2070,17 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Effort (md)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Philippine market where relevant</t>
+          <t>Zero: offered OOTB</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -1885,57 +2088,57 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Interface or data load</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Indicative; not in the CR total</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr"/>
+          <t>Integration or Data Migration</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope, Data Migration scope</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>BRD ID</t>
+          <t>What</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>What is exchanged or loaded</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr"/>
@@ -1943,17 +2146,17 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>Where in the FRS</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Text of the BRD</t>
+          <t>Annex</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -1961,17 +2164,17 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fit class of the fit-gap workbook</t>
+          <t>Best practice</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -1979,17 +2182,17 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>What iNXT BrokerVerse offers out of the box</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>OOTB capability</t>
+          <t>Insurance-broking practice</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -1997,23 +2200,153 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Philippine market where relevant</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Indicative; not in the CR total</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
           <t>BRD items to deliver</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>BRD ID</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Text of the BRD</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Fit class of the fit-gap workbook</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>What iNXT BrokerVerse offers out of the box</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>OOTB capability</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Planning man-days</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>For the points of BDOI's FRS covered by a BRD line</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D52"/>
+  <autoFilter ref="A4:D59"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2034,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2078,154 +2411,164 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Change requests (orange)</t>
+          <t>BRD requirements offered OOTB (black, in scope, no effort)</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
+          <t>Change requests (orange)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
           <t>Man-days: Analysis &amp; design</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B8" s="12">
         <f>SUM('CR Effort'!M5:M6)</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Man-days: Backend</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B9" s="12">
         <f>SUM('CR Effort'!N5:N6)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Man-days: Frontend</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B10" s="12">
         <f>SUM('CR Effort'!O5:O6)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Man-days: Testing</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B11" s="12">
         <f>SUM('CR Effort'!P5:P6)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Man-days: Documentation / UAT support</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B12" s="12">
         <f>SUM('CR Effort'!Q5:Q6)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Total change request man-days</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B13" s="12">
         <f>SUM('CR Effort'!R5:R6)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Range low (-20%)</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B14" s="12">
         <f>SUM('CR Effort'!S5:S6)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Range high (+20%)</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B15" s="12">
         <f>SUM('CR Effort'!T5:T6)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Cost in PHP at the day rate of the Assumptions sheet</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B16" s="12">
         <f>SUM('CR Effort'!U5:U6)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>29</v>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Best-practice recommendations (blue; indicative, not in the CR total)</t>
+          <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>Best-practice recommendations (blue; indicative, not in the CR total)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
           <t>Best-practice indicative man-days (not in the CR total)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B19" s="12" t="n">
         <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B18"/>
+  <autoFilter ref="A4:B19"/>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B518">
+  <conditionalFormatting sqref="A5:B519">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2777,7 +3120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2852,17 +3195,17 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-01b</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Scheduled daily run of the Daily Cash Reconciliation Reports</t>
+          <t>Scheduled weekly run of the Unapplied Premium Payment Transaction report</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRS.CSH.09.02.10; Appendix M</t>
+          <t>FRS.CSH.09.02.11; Appendix M</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -2884,47 +3227,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>G-01b</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Scheduled weekly run of the Unapplied Premium Payment Transaction report</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>FRS.CSH.09.02.11; Appendix M</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>RPT-007 Available (user-scheduled reports with recipients)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Reports &gt; Schedules: timing, format and recipients</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G6"/>
+  <autoFilter ref="A4:G5"/>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G506">
+  <conditionalFormatting sqref="A5:G505">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2944,6 +3252,143 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>BRD covered - OOTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse OOTB platform provides: no change request, no effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>BRD line</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Effort (md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Scheduled daily run of the Daily Cash Reconciliation Reports</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>FRS.CSH.09.02.10; Appendix M</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>CSHID.023 "Capability to generate reports. See Cashiering Reports list under Annex"; Report List (Operations - Cashiering): "Daily Cash Reconciliation Reports - Summarizes daily cash receipts and deposits", frequency "Daily"</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>RPT-007 Available (user-scheduled reports with recipients)</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Reports &gt; Schedules: timing, format and recipients</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G505">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3667,7 +4112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3835,7 +4280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5098,192 +5543,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Hours in a man-day</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>One man-day (md) = 8 working hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>Philippine peso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Estimate range (plus or minus)</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
-        <is>
-          <t>Each total is an estimate within plus or minus 20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>DayRate (PHP per man-day)</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="25" t="inlineStr">
-        <is>
-          <t>Enter the agreed day rate; the cost columns follow by formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>OOTB baseline</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>brokerverse-platform</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>Platform size</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>Not change requests</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="inlineStr">
-        <is>
-          <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>30 days</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Estimated again if the scope of a change request changes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
@@ -20,11 +20,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -690,13 +690,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -725,6 +728,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -797,6 +801,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -954,6 +959,8 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="15" t="inlineStr">
         <is>
@@ -1009,6 +1016,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -1290,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1313,6 +1321,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1545,12 +1554,12 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
+          <t>Effort covers</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Yes / No / Partly, with what was done for BIBS in this project (the effort is given anyway: the value of the change request)</t>
+          <t>For a Partial feature: the missing part only</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -1563,12 +1572,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Effort covers</t>
+          <t>Estimate basis</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>For a Partial feature: the missing part only</t>
+          <t>Size of the platform parts the change touches</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1581,12 +1590,12 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Estimate basis</t>
+          <t>Analysis &amp; design (md)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Size of the platform parts the change touches</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -1599,7 +1608,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Analysis &amp; design (md)</t>
+          <t>Backend (md)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1617,7 +1626,7 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Backend (md)</t>
+          <t>Frontend (md)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -1635,7 +1644,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Frontend (md)</t>
+          <t>Testing (md)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -1653,7 +1662,7 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Testing (md)</t>
+          <t>Documentation / UAT support (md)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -1671,12 +1680,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Documentation / UAT support (md)</t>
+          <t>Total (md)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Sum of the activities</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -1689,12 +1698,12 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Total (md)</t>
+          <t>Low (-20%)</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Sum of the activities</t>
+          <t>Total less the range</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr"/>
@@ -1707,12 +1716,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Low (-20%)</t>
+          <t>High (+20%)</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Total less the range</t>
+          <t>Total plus the range</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
@@ -1725,12 +1734,12 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>High (+20%)</t>
+          <t>Cost (PHP)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Total plus the range</t>
+          <t>Total x day rate (Assumptions)</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr"/>
@@ -1743,15 +1752,19 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Cost (PHP)</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Total x day rate (Assumptions)</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr"/>
+          <t>Low / Medium / High</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Low, Medium, High</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -1761,17 +1774,17 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Low / Medium / High</t>
+          <t>High / Medium / Low</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Low, Medium, High</t>
+          <t>High, Medium, Low</t>
         </is>
       </c>
     </row>
@@ -1783,19 +1796,15 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>What the change needs first</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -1805,12 +1814,12 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>What the change needs first</t>
+          <t>Scope assumed by the estimate</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr"/>
@@ -1818,17 +1827,17 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>CR Effort</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Scope assumed by the estimate</t>
+          <t>Point (Appendix W.3)</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
@@ -1841,12 +1850,12 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Point (Appendix W.3)</t>
+          <t>The point of the FRS</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -1859,12 +1868,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>The point of the FRS</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -1877,12 +1886,12 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>FR item or annex</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr"/>
@@ -1895,12 +1904,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Programme Feature List, column OOTB platform</t>
+          <t>Screen or function of brokerverse-platform</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr"/>
@@ -1913,12 +1922,12 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
+          <t>BRD reference</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Screen or function of brokerverse-platform</t>
+          <t>Not in the BRD</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr"/>
@@ -1931,12 +1940,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>BRD reference</t>
+          <t>Cost (md)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Not in the BRD</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -1944,17 +1953,17 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Cost (md)</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Former green point</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -1967,12 +1976,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Former green point</t>
+          <t>The point of the FRS</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -1985,12 +1994,12 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>The point of the FRS</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2003,12 +2012,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>BRD line</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex</t>
+          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2021,12 +2030,12 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>BRD line</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2039,12 +2048,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Programme Feature List, column OOTB platform</t>
+          <t>Screen or function of brokerverse-platform</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2057,12 +2066,12 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
+          <t>Effort (md)</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Screen or function of brokerverse-platform</t>
+          <t>Zero: offered OOTB</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2070,17 +2079,17 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>BRD covered - OOTB</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Effort (md)</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Zero: offered OOTB</t>
+          <t>Interface or data load</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2093,15 +2102,19 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Interface or data load</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr"/>
+          <t>Integration or Data Migration</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Integration scope, Data Migration scope</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -2111,19 +2124,15 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>What</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Integration or Data Migration</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>Integration scope, Data Migration scope</t>
-        </is>
-      </c>
+          <t>What is exchanged or loaded</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -2133,12 +2142,12 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Where in the FRS</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>What is exchanged or loaded</t>
+          <t>Annex</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr"/>
@@ -2146,17 +2155,17 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Where in the FRS</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Annex</t>
+          <t>Best practice</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2169,12 +2178,12 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Best practice</t>
+          <t>Insurance-broking practice</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -2187,12 +2196,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Why it matters for a broker</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Insurance-broking practice</t>
+          <t>Philippine market where relevant</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2205,15 +2214,19 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Suggested priority</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Philippine market where relevant</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr"/>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -2223,34 +2236,30 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>Indicative man-days</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Indicative; not in the CR total</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
+          <t>BRD ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Indicative; not in the CR total</t>
+          <t>BRD requirement</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2263,12 +2272,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>BRD ID</t>
+          <t>BRD requirement</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>Text of the BRD</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2281,12 +2290,12 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Text of the BRD</t>
+          <t>Fit class of the fit-gap workbook</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2299,12 +2308,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Fit class of the fit-gap workbook</t>
+          <t>OOTB capability</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2317,36 +2326,18 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>What iNXT BrokerVerse offers out of the box</t>
+          <t>Planning man-days</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>OOTB capability</t>
+          <t>For the points of BDOI's FRS covered by a BRD line</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>BRD items to deliver</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Planning man-days</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>For the points of BDOI's FRS covered by a BRD line</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D59"/>
+  <autoFilter ref="A4:D58"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2441,87 +2432,87 @@
         </is>
       </c>
       <c r="B8" s="12">
+        <f>SUM('CR Effort'!L5:L6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Backend</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
         <f>SUM('CR Effort'!M5:M6)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Backend</t>
-        </is>
-      </c>
-      <c r="B9" s="12">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Frontend</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
         <f>SUM('CR Effort'!N5:N6)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Frontend</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Testing</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
         <f>SUM('CR Effort'!O5:O6)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Testing</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Documentation / UAT support</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
         <f>SUM('CR Effort'!P5:P6)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Documentation / UAT support</t>
-        </is>
-      </c>
-      <c r="B12" s="12">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Total change request man-days</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
         <f>SUM('CR Effort'!Q5:Q6)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Total change request man-days</t>
-        </is>
-      </c>
-      <c r="B13" s="12">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Range low (-20%)</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
         <f>SUM('CR Effort'!R5:R6)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Range low (-20%)</t>
-        </is>
-      </c>
-      <c r="B14" s="12">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Range high (+20%)</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
         <f>SUM('CR Effort'!S5:S6)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Range high (+20%)</t>
-        </is>
-      </c>
-      <c r="B15" s="12">
-        <f>SUM('CR Effort'!T5:T6)</f>
-        <v/>
-      </c>
-    </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
@@ -2529,7 +2520,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>SUM('CR Effort'!U5:U6)</f>
+        <f>SUM('CR Effort'!T5:T6)</f>
         <v/>
       </c>
     </row>
@@ -2593,7 +2584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2605,22 +2596,21 @@
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
-    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2662,7 +2652,6 @@
       <c r="V3" s="20" t="n"/>
       <c r="W3" s="20" t="n"/>
       <c r="X3" s="20" t="n"/>
-      <c r="Y3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -2712,80 +2701,75 @@
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
+          <t>Effort covers</t>
         </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>Effort covers</t>
+          <t>Estimate basis</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>Estimate basis</t>
+          <t>Analysis &amp; design (md)</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t>Analysis &amp; design (md)</t>
+          <t>Backend (md)</t>
         </is>
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>Backend (md)</t>
+          <t>Frontend (md)</t>
         </is>
       </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>Frontend (md)</t>
+          <t>Testing (md)</t>
         </is>
       </c>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t>Testing (md)</t>
+          <t>Documentation / UAT support (md)</t>
         </is>
       </c>
       <c r="Q4" s="21" t="inlineStr">
         <is>
-          <t>Documentation / UAT support (md)</t>
+          <t>Total (md)</t>
         </is>
       </c>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t>Total (md)</t>
+          <t>Low (-20%)</t>
         </is>
       </c>
       <c r="S4" s="21" t="inlineStr">
         <is>
-          <t>Low (-20%)</t>
+          <t>High (+20%)</t>
         </is>
       </c>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t>High (+20%)</t>
+          <t>Cost (PHP)</t>
         </is>
       </c>
       <c r="U4" s="21" t="inlineStr">
         <is>
-          <t>Cost (PHP)</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="V4" s="21" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="W4" s="21" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="X4" s="21" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="Y4" s="21" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
@@ -2839,49 +2823,49 @@
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>No: BIBS shows the records For Posting and For Approval with their age, without a time rule</t>
+          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: time rules, overdue marker and reminder for the Cashiering stages.</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: time rules, overdue marker and reminder for the Cashiering stages.</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
           <t>Turnaround parts of the platform reused; Cashiering decision services and dashboard counts extended.</t>
         </is>
       </c>
+      <c r="L5" s="22" t="n">
+        <v>1</v>
+      </c>
       <c r="M5" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="22" t="n">
-        <v>2.5</v>
-      </c>
       <c r="O5" s="22" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="P5" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q5" s="22" t="n">
         <v>0.5</v>
       </c>
+      <c r="Q5" s="22">
+        <f>SUM(L5:P5)</f>
+        <v/>
+      </c>
       <c r="R5" s="22">
-        <f>SUM(M5:Q5)</f>
+        <f>ROUND(Q5*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
       <c r="S5" s="22">
-        <f>ROUND(R5*(1-Assumptions!$B$6),1)</f>
+        <f>ROUND(Q5*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="T5" s="22">
-        <f>ROUND(R5*(1+Assumptions!$B$6),1)</f>
+      <c r="T5" s="23">
+        <f>Q5*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="U5" s="23">
-        <f>R5*Assumptions!$B$7</f>
-        <v/>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="V5" s="12" t="inlineStr">
         <is>
@@ -2890,15 +2874,10 @@
       </c>
       <c r="W5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>BDOI to confirm the times (Appendix R, Appendix S)</t>
         </is>
       </c>
       <c r="X5" s="12" t="inlineStr">
-        <is>
-          <t>BDOI to confirm the times (Appendix R, Appendix S)</t>
-        </is>
-      </c>
-      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>Four stages (posting, cancellation / reinstatement posting, disposition, approval); times as parameters; one reminder to the poster or approver; no escalation.</t>
         </is>
@@ -2952,49 +2931,49 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>Yes: the Notification Settings screen of BIBS gives this choice</t>
+          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Partial in BrokerVerse OOTB; the effort is that of the missing part (per-user, per-notice e-mail choice).</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
           <t>Notification service of the platform; one settings screen.</t>
         </is>
       </c>
+      <c r="L6" s="22" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M6" s="22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N6" s="22" t="n">
         <v>1</v>
       </c>
       <c r="O6" s="22" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P6" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q6" s="22" t="n">
-        <v>0.5</v>
+      <c r="Q6" s="22">
+        <f>SUM(L6:P6)</f>
+        <v/>
       </c>
       <c r="R6" s="22">
-        <f>SUM(M6:Q6)</f>
+        <f>ROUND(Q6*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
       <c r="S6" s="22">
-        <f>ROUND(R6*(1-Assumptions!$B$6),1)</f>
+        <f>ROUND(Q6*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="T6" s="22">
-        <f>ROUND(R6*(1+Assumptions!$B$6),1)</f>
+      <c r="T6" s="23">
+        <f>Q6*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="U6" s="23">
-        <f>R6*Assumptions!$B$7</f>
-        <v/>
+      <c r="U6" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
       </c>
       <c r="V6" s="12" t="inlineStr">
         <is>
@@ -3003,15 +2982,10 @@
       </c>
       <c r="W6" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>E-mail channel of BDOI</t>
         </is>
       </c>
       <c r="X6" s="12" t="inlineStr">
-        <is>
-          <t>E-mail channel of BDOI</t>
-        </is>
-      </c>
-      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>Choice per user and per notice type; default in-app only.</t>
         </is>
@@ -3037,7 +3011,10 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="12" t="n"/>
+      <c r="L7" s="22">
+        <f>SUM(L5:L6)</f>
+        <v/>
+      </c>
       <c r="M7" s="22">
         <f>SUM(M5:M6)</f>
         <v/>
@@ -3066,25 +3043,21 @@
         <f>SUM(S5:S6)</f>
         <v/>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="23">
         <f>SUM(T5:T6)</f>
         <v/>
       </c>
-      <c r="U7" s="23">
-        <f>SUM(U5:U6)</f>
-        <v/>
-      </c>
+      <c r="U7" s="12" t="n"/>
       <c r="V7" s="12" t="n"/>
       <c r="W7" s="12" t="n"/>
       <c r="X7" s="12" t="n"/>
-      <c r="Y7" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y7"/>
+  <autoFilter ref="A4:X7"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A2:X2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:Y507">
+  <conditionalFormatting sqref="A5:X507">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3093,10 +3066,10 @@
     <dataValidation sqref="E5:E507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="V5:V507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="U5:U507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="W5:W507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="V5:V507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -3580,7 +3553,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Channel simulator (SIT and UAT only)</t>
+          <t>Test files of the payment channels (SIT and UAT)</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
@@ -4937,7 +4910,7 @@
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
+          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of the platform.</t>
         </is>
       </c>
       <c r="E30" s="12" t="n"/>
@@ -4960,7 +4933,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of BIBS, available in the BIBS environment.</t>
+          <t>Unapplied workbench with disposition types, approval rule per type, tabs by status, reversal and refund to Disbursement is an extension of the platform.</t>
         </is>
       </c>
       <c r="E31" s="12" t="n"/>
@@ -5075,7 +5048,7 @@
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Within the BIBS sizing for all BRDs</t>
+          <t>Within the programme sizing for all BRDs</t>
         </is>
       </c>
       <c r="E36" s="12" t="n"/>
@@ -5098,7 +5071,7 @@
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Assumed within the BIBS sizing; to confirm</t>
+          <t>Assumed within the programme sizing; to confirm</t>
         </is>
       </c>
       <c r="E37" s="12" t="n"/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
@@ -20,6 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="Accuracy">Assumptions!$B$6</definedName>
+    <definedName name="DayRate">Assumptions!$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
@@ -36,6 +38,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BRD items to deliver'!$A$4:$E$55</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Assumptions'!$A$3:$C$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Assumptions'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -194,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -233,7 +237,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -984,7 +994,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -999,7 +1009,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1018,169 +1028,179 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Hours in a man-day</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>One man-day (md) = 8 working hours</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>PHP</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Philippine peso</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Estimate range (plus or minus)</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="28" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Each total is an estimate within plus or minus 20%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>DayRate (PHP per man-day)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Enter the agreed day rate; the cost columns follow by formula</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>OOTB baseline</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>brokerverse-platform</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Platform size</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Not change requests</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Validity</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Estimated again if the scope of a change request changes</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 &amp;K656565&amp;F</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1200,78 +1220,78 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>BRD relation</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="D1" s="24" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>Extends a BRD requirement</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C2" s="28" t="inlineStr">
+      <c r="C2" s="30" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D2" s="28" t="inlineStr">
+      <c r="D2" s="30" t="inlineStr">
         <is>
           <t>Integration scope</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>Not in any BRD</t>
         </is>
       </c>
-      <c r="B3" s="28" t="inlineStr">
+      <c r="B3" s="30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" s="28" t="inlineStr">
+      <c r="D3" s="30" t="inlineStr">
         <is>
           <t>Data Migration scope</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1282,7 +1302,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2342,7 +2362,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2401,7 +2421,7 @@
           <t>Points beyond the BRD available OOTB (green, no cost)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2431,7 +2451,7 @@
           <t>Man-days: Analysis &amp; design</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="23">
         <f>SUM('CR Effort'!L5:L6)</f>
         <v/>
       </c>
@@ -2442,7 +2462,7 @@
           <t>Man-days: Backend</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="23">
         <f>SUM('CR Effort'!M5:M6)</f>
         <v/>
       </c>
@@ -2453,7 +2473,7 @@
           <t>Man-days: Frontend</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="23">
         <f>SUM('CR Effort'!N5:N6)</f>
         <v/>
       </c>
@@ -2464,7 +2484,7 @@
           <t>Man-days: Testing</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="23">
         <f>SUM('CR Effort'!O5:O6)</f>
         <v/>
       </c>
@@ -2475,7 +2495,7 @@
           <t>Man-days: Documentation / UAT support</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="23">
         <f>SUM('CR Effort'!P5:P6)</f>
         <v/>
       </c>
@@ -2486,7 +2506,7 @@
           <t>Total change request man-days</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="23">
         <f>SUM('CR Effort'!Q5:Q6)</f>
         <v/>
       </c>
@@ -2497,7 +2517,7 @@
           <t>Range low (-20%)</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="23">
         <f>SUM('CR Effort'!R5:R6)</f>
         <v/>
       </c>
@@ -2508,7 +2528,7 @@
           <t>Range high (+20%)</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="23">
         <f>SUM('CR Effort'!S5:S6)</f>
         <v/>
       </c>
@@ -2519,7 +2539,7 @@
           <t>Cost in PHP at the day rate of the Assumptions sheet</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="22">
         <f>SUM('CR Effort'!T5:T6)</f>
         <v/>
       </c>
@@ -2530,7 +2550,7 @@
           <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="22" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2550,7 +2570,7 @@
           <t>Best-practice indicative man-days (not in the CR total)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="23" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2568,7 +2588,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2831,34 +2851,34 @@
           <t>Turnaround parts of the platform reused; Cashiering decision services and dashboard counts extended.</t>
         </is>
       </c>
-      <c r="L5" s="22" t="n">
+      <c r="L5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="24" t="n">
         <v>2.5</v>
       </c>
-      <c r="N5" s="22" t="n">
+      <c r="N5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O5" s="22" t="n">
+      <c r="O5" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="P5" s="22" t="n">
+      <c r="P5" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5" s="24">
         <f>SUM(L5:P5)</f>
         <v/>
       </c>
-      <c r="R5" s="22">
+      <c r="R5" s="24">
         <f>ROUND(Q5*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="S5" s="22">
+      <c r="S5" s="24">
         <f>ROUND(Q5*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="T5" s="23">
+      <c r="T5" s="25">
         <f>Q5*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -2939,34 +2959,34 @@
           <t>Notification service of the platform; one settings screen.</t>
         </is>
       </c>
-      <c r="L6" s="22" t="n">
+      <c r="L6" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="M6" s="22" t="n">
+      <c r="M6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="22" t="n">
+      <c r="N6" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="22" t="n">
+      <c r="O6" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="P6" s="22" t="n">
+      <c r="P6" s="24" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="24">
         <f>SUM(L6:P6)</f>
         <v/>
       </c>
-      <c r="R6" s="22">
+      <c r="R6" s="24">
         <f>ROUND(Q6*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="S6" s="22">
+      <c r="S6" s="24">
         <f>ROUND(Q6*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="T6" s="23">
+      <c r="T6" s="25">
         <f>Q6*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -3011,39 +3031,39 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="12" t="n"/>
-      <c r="L7" s="22">
+      <c r="L7" s="24">
         <f>SUM(L5:L6)</f>
         <v/>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="24">
         <f>SUM(M5:M6)</f>
         <v/>
       </c>
-      <c r="N7" s="22">
+      <c r="N7" s="24">
         <f>SUM(N5:N6)</f>
         <v/>
       </c>
-      <c r="O7" s="22">
+      <c r="O7" s="24">
         <f>SUM(O5:O6)</f>
         <v/>
       </c>
-      <c r="P7" s="22">
+      <c r="P7" s="24">
         <f>SUM(P5:P6)</f>
         <v/>
       </c>
-      <c r="Q7" s="22">
+      <c r="Q7" s="24">
         <f>SUM(Q5:Q6)</f>
         <v/>
       </c>
-      <c r="R7" s="22">
+      <c r="R7" s="24">
         <f>SUM(R5:R6)</f>
         <v/>
       </c>
-      <c r="S7" s="22">
+      <c r="S7" s="24">
         <f>SUM(S5:S6)</f>
         <v/>
       </c>
-      <c r="T7" s="23">
+      <c r="T7" s="25">
         <f>SUM(T5:T6)</f>
         <v/>
       </c>
@@ -3077,7 +3097,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3196,7 +3216,7 @@
           <t>Not in BRD</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3214,7 +3234,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3333,7 +3353,7 @@
           <t>Reports &gt; Schedules: timing, format and recipients</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,7 +3371,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4075,7 +4095,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4170,7 +4190,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4195,7 +4215,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="23" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4220,7 +4240,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="23" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4243,7 +4263,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5465,7 +5485,7 @@
           <t>WFL-013 Partial (a failed job raises an in-app notification to the schedule administrators; no e-mail to a recipient list). Partial in BrokerVerse OOTB; the planning effort is that of the missing part (e-mail to a recipient list).</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="E54" s="23" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -5490,7 +5510,7 @@
           <t>BIL-016 Available (receipts register with filters); RPT-003 Partial. Disagreement: the Feature List says Available, the OOTB code exports the receipt list to PDF only. Partial in BrokerVerse OOTB; the planning effort is that of the missing part (Excel export of the lists).</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E55" s="23" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5508,7 +5528,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-02_Operations_Cashiering/BIBS_CR_BRD-02_Effort_Estimate_v1.0.xlsx
@@ -3095,7 +3095,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
